--- a/mindcraft_funnel_tracker.xlsx
+++ b/mindcraft_funnel_tracker.xlsx
@@ -4434,7 +4434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="30" min="1" max="1"/>
@@ -4735,307 +4735,339 @@
     <row r="16" ht="60" customHeight="1" s="30">
       <c r="A16" s="83" t="inlineStr">
         <is>
-          <t>Quality flags</t>
+          <t>Critical feedback (Day 26 + share page)</t>
         </is>
       </c>
       <c r="B16" s="44" t="inlineStr">
         <is>
-          <t>FlagButton (in-app, on AI outputs)</t>
+          <t>/day/26 (TellTab) + /share feedback tab</t>
         </is>
       </c>
       <c r="C16" s="44" t="inlineStr">
         <is>
-          <t>quality_flags</t>
+          <t>feedback_entries</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>output_type, framework_name, flag_reason, user_comment</t>
+          <t>user_id, enrollment_id, day_number, source (day_26_prompt | share_page_feedback_tab | other), body, created_at</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>User-flagged AI outputs (off tone, inaccurate, etc.)</t>
+          <t>THE most important table for product improvement. Service-role-only RLS. Auto-mirror from journal Day 26 via useStep2Journal.ts</t>
         </is>
       </c>
       <c r="F16" s="84" t="inlineStr">
         <is>
-          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=quality_flags&amp;sort=created_at.desc</t>
+          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=feedback_entries&amp;sort=created_at.desc</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1" s="30">
       <c r="A17" s="83" t="inlineStr">
         <is>
-          <t>Weekly review reflections + NPS</t>
+          <t>Quality flags</t>
         </is>
       </c>
       <c r="B17" s="44" t="inlineStr">
         <is>
-          <t>/weekly-review</t>
+          <t>FlagButton (in-app, on AI outputs)</t>
         </is>
       </c>
       <c r="C17" s="44" t="inlineStr">
         <is>
-          <t>weekly_reviews</t>
+          <t>quality_flags</t>
         </is>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>reflection, plan_adjustments, goal_ratings (jsonb), nps_score, week_number, top_themes</t>
+          <t>output_type, framework_name, flag_reason, user_comment</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Includes NPS score per week</t>
+          <t>User-flagged AI outputs (off tone, inaccurate, etc.)</t>
         </is>
       </c>
       <c r="F17" s="84" t="inlineStr">
         <is>
-          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=weekly_reviews&amp;sort=created_at.desc</t>
+          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=quality_flags&amp;sort=created_at.desc</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1" s="30">
       <c r="A18" s="83" t="inlineStr">
         <is>
-          <t>Daily journal entries + ratings</t>
+          <t>Weekly review reflections + NPS</t>
         </is>
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>/day/[N] (TellTab + DoneTab)</t>
+          <t>/weekly-review</t>
         </is>
       </c>
       <c r="C18" s="44" t="inlineStr">
         <is>
-          <t>daily_sessions</t>
+          <t>weekly_reviews</t>
         </is>
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>step_2_journal, day_rating, day_feedback, completed_at</t>
+          <t>reflection, plan_adjustments, goal_ratings (jsonb), nps_score, week_number, top_themes</t>
         </is>
       </c>
       <c r="E18" s="35" t="inlineStr">
         <is>
-          <t>One row per day per enrollment</t>
+          <t>Includes NPS score per week</t>
         </is>
       </c>
       <c r="F18" s="84" t="inlineStr">
         <is>
-          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=daily_sessions&amp;sort=completed_at.desc</t>
+          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=weekly_reviews&amp;sort=created_at.desc</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1" s="30">
       <c r="A19" s="83" t="inlineStr">
         <is>
-          <t>Exercise responses + star ratings</t>
+          <t>Daily journal entries + ratings</t>
         </is>
       </c>
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>/day/[N] (DoTab)</t>
+          <t>/day/[N] (TellTab + DoneTab)</t>
         </is>
       </c>
       <c r="C19" s="44" t="inlineStr">
         <is>
-          <t>exercise_completions</t>
+          <t>daily_sessions</t>
         </is>
       </c>
       <c r="D19" s="35" t="inlineStr">
         <is>
-          <t>framework_name, exercise_type, modality, responses (jsonb), star_rating, feedback</t>
+          <t>step_2_journal, day_rating, day_feedback, completed_at</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Per-exercise structured + freeform feedback</t>
+          <t>One row per day per enrollment</t>
         </is>
       </c>
       <c r="F19" s="84" t="inlineStr">
         <is>
-          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=exercise_completions&amp;sort=completed_at.desc</t>
+          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=daily_sessions&amp;sort=completed_at.desc</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1" s="30">
       <c r="A20" s="83" t="inlineStr">
         <is>
-          <t>Final program insights</t>
+          <t>Exercise responses + star ratings</t>
         </is>
       </c>
       <c r="B20" s="44" t="inlineStr">
         <is>
-          <t>/insights/final</t>
+          <t>/day/[N] (DoTab)</t>
         </is>
       </c>
       <c r="C20" s="44" t="inlineStr">
         <is>
-          <t>final_insights</t>
+          <t>exercise_completions</t>
         </is>
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
-          <t>content (AI-generated), status, program_slug, generated_at</t>
+          <t>framework_name, exercise_type, modality, responses (jsonb), star_rating, feedback</t>
         </is>
       </c>
       <c r="E20" s="35" t="inlineStr">
         <is>
-          <t>Generated at program off-ramp</t>
+          <t>Per-exercise structured + freeform feedback</t>
         </is>
       </c>
       <c r="F20" s="84" t="inlineStr">
         <is>
-          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=final_insights&amp;sort=created_at.desc</t>
+          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=exercise_completions&amp;sort=completed_at.desc</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1" s="30">
       <c r="A21" s="83" t="inlineStr">
         <is>
+          <t>Final program insights</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>/insights/final</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>final_insights</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>content (AI-generated), status, program_slug, generated_at</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Generated at program off-ramp</t>
+        </is>
+      </c>
+      <c r="F21" s="84" t="inlineStr">
+        <is>
+          <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=final_insights&amp;sort=created_at.desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="83" t="inlineStr">
+        <is>
           <t>Waitlist signups</t>
         </is>
       </c>
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>Homepage ComingSoonWaitlist + /assessment fallback</t>
         </is>
       </c>
-      <c r="C21" s="44" t="inlineStr">
+      <c r="C22" s="44" t="inlineStr">
         <is>
           <t>waitlist_signups</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>email, program (free-text — assessment quiz scores legacy-flattened here)</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>Assessment scores now in assessment_responses; this stays for waitlist signups</t>
         </is>
       </c>
-      <c r="F21" s="84" t="inlineStr">
+      <c r="F22" s="84" t="inlineStr">
         <is>
           <t>https://supabase.com/dashboard/project/rmdjglepocaswpplwgik/editor?table=waitlist_signups&amp;sort=created_at.desc</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23"/>
-    <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>WEEKLY QUALITATIVE REVIEW — copy each Monday</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="40" t="inlineStr">
+    <row r="26" ht="30" customHeight="1" s="30">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1" s="30">
-      <c r="A26" s="83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>Open Supabase coaching_applications. Filter status=new. Triage each one — mark reviewing/qualified/declined.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="30">
       <c r="A27" s="83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" s="35" t="inlineStr">
         <is>
-          <t>Open exit_surveys. Read every new row. Tag the most common reasons. Look for the comeback_text patterns.</t>
+          <t>Open Supabase coaching_applications. Filter status=new. Triage each one — mark reviewing/qualified/declined.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="30">
       <c r="A28" s="83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B28" s="35" t="inlineStr">
         <is>
-          <t>Open testimonial_surveys. For permission_given=true rows, decide which to promote to the public testimonials table.</t>
+          <t>Open exit_surveys. Read every new row. Tag the most common reasons. Look for the comeback_text patterns.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="30">
       <c r="A29" s="83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B29" s="35" t="inlineStr">
         <is>
-          <t>Open assessment_responses. Look at avg_score distribution and top_disruptions. Are people scoring low on the same things consistently?</t>
+          <t>Open testimonial_surveys. For permission_given=true rows, decide which to promote to the public testimonials table.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="30">
       <c r="A30" s="83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B30" s="35" t="inlineStr">
         <is>
-          <t>Open weekly_reviews. Read reflection + plan_adjustments. Note the NPS score average for the week.</t>
+          <t>Open assessment_responses. Look at avg_score distribution and top_disruptions. Are people scoring low on the same things consistently?</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="30">
       <c r="A31" s="83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>Open quality_flags. Are the same exercises getting flagged repeatedly? That's an exercise-design problem.</t>
+          <t>Open weekly_reviews. Read reflection + plan_adjustments. Note the NPS score average for the week.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="30">
       <c r="A32" s="83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B32" s="35" t="inlineStr">
         <is>
-          <t>Open daily_sessions. Skim day_feedback (the freeform field). Patterns?</t>
+          <t>Open quality_flags. Are the same exercises getting flagged repeatedly? That's an exercise-design problem.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="30">
       <c r="A33" s="83" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>Open daily_sessions. Skim day_feedback (the freeform field). Patterns?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="83" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Open exercise_completions where star_rating is not null. Sort by lowest rating. Read the feedback column.</t>
         </is>
@@ -5066,11 +5098,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
